--- a/SGC-CKN/Excel/7dcc13a2-91b9-40ff-bac6-1a43c9a1d316_Lô_đất_ký_hiệu_CT-02_15_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/7dcc13a2-91b9-40ff-bac6-1a43c9a1d316_Lô_đất_ký_hiệu_CT-02_15_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>15</t>
+    <t>P1-157</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -157,6 +157,9 @@
   <si>
     <t xml:space="preserve">11:15
 19/03/2026</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
@@ -1337,19 +1340,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-25.5</v>
@@ -1372,19 +1375,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" s="28">
         <v>-39.73</v>
@@ -1407,7 +1410,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1513,31 +1516,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1722,7 +1725,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1751,7 +1754,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1774,7 +1777,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>

--- a/SGC-CKN/Excel/7dcc13a2-91b9-40ff-bac6-1a43c9a1d316_Lô_đất_ký_hiệu_CT-02_15_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/7dcc13a2-91b9-40ff-bac6-1a43c9a1d316_Lô_đất_ký_hiệu_CT-02_15_D800_19-03-2026.xlsx
@@ -165,7 +165,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">14:45
+    <t xml:space="preserve">11:45
 19/03/2026</t>
   </si>
   <si>
@@ -355,17 +355,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -532,26 +532,26 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1288,16 +1288,16 @@
         <v>-16</v>
       </c>
       <c r="G15" s="18">
-        <v>-24.2</v>
+        <v>-21.2</v>
       </c>
       <c r="H15" s="18">
         <v>0.25</v>
       </c>
       <c r="I15" s="18">
-        <v>8.2</v>
+        <v>5.2</v>
       </c>
       <c r="J15" s="8">
-        <v>32.8</v>
+        <v>20.8</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1320,7 +1320,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="21">
-        <v>-24.2</v>
+        <v>-21.2</v>
       </c>
       <c r="G16" s="21">
         <v>-25.5</v>
@@ -1329,82 +1329,82 @@
         <v>0.33</v>
       </c>
       <c r="I16" s="21">
-        <v>1.3</v>
-      </c>
-      <c r="J16" s="24">
-        <v>3.9</v>
+        <v>4.3</v>
+      </c>
+      <c r="J16" s="8">
+        <v>12.9</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>-25.5</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>-39.73</v>
       </c>
-      <c r="H17" s="25">
-        <v>3.5</v>
-      </c>
-      <c r="I17" s="25">
+      <c r="H17" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="24">
         <v>14.23</v>
       </c>
-      <c r="J17" s="24">
-        <v>4.07</v>
-      </c>
-      <c r="K17" s="26" t="s">
+      <c r="J17" s="8">
+        <v>28.46</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="27">
         <v>-39.73</v>
       </c>
-      <c r="G18" s="28">
-        <v>-44.25</v>
-      </c>
-      <c r="H18" s="28">
-        <v>0.75</v>
-      </c>
-      <c r="I18" s="28">
-        <v>4.52</v>
-      </c>
-      <c r="J18" s="8">
-        <v>6.03</v>
-      </c>
-      <c r="K18" s="29" t="s">
+      <c r="G18" s="27">
+        <v>-44.23</v>
+      </c>
+      <c r="H18" s="27">
+        <v>3.75</v>
+      </c>
+      <c r="I18" s="27">
+        <v>4.5</v>
+      </c>
+      <c r="J18" s="30">
+        <v>1.2</v>
+      </c>
+      <c r="K18" s="28" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1676,16 +1676,16 @@
         <v>-16</v>
       </c>
       <c r="F6" s="18">
-        <v>-24.2</v>
+        <v>-21.2</v>
       </c>
       <c r="G6" s="18">
         <v>0.25</v>
       </c>
       <c r="H6" s="18">
-        <v>8.2</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="8">
-        <v>32.8</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1702,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-24.2</v>
+        <v>-21.2</v>
       </c>
       <c r="F7" s="21">
         <v>-25.5</v>
@@ -1711,68 +1711,68 @@
         <v>0.33</v>
       </c>
       <c r="H7" s="21">
-        <v>1.3</v>
-      </c>
-      <c r="I7" s="24">
-        <v>3.9</v>
+        <v>4.3</v>
+      </c>
+      <c r="I7" s="8">
+        <v>12.9</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>-25.5</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <v>-39.73</v>
       </c>
-      <c r="G8" s="25">
-        <v>3.5</v>
-      </c>
-      <c r="H8" s="25">
+      <c r="G8" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="24">
         <v>14.23</v>
       </c>
-      <c r="I8" s="24">
-        <v>4.07</v>
+      <c r="I8" s="8">
+        <v>28.46</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="27">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <v>-39.73</v>
       </c>
-      <c r="F9" s="28">
-        <v>-44.25</v>
-      </c>
-      <c r="G9" s="28">
-        <v>0.75</v>
-      </c>
-      <c r="H9" s="28">
-        <v>4.52</v>
-      </c>
-      <c r="I9" s="8">
-        <v>6.03</v>
+      <c r="F9" s="27">
+        <v>-44.23</v>
+      </c>
+      <c r="G9" s="27">
+        <v>3.75</v>
+      </c>
+      <c r="H9" s="27">
+        <v>4.5</v>
+      </c>
+      <c r="I9" s="30">
+        <v>1.2</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1792,16 +1792,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-44.25</v>
+        <v>-44.23</v>
       </c>
       <c r="G10" s="33">
         <v>5.83</v>
       </c>
       <c r="H10" s="33">
-        <v>44.25</v>
+        <v>44.23</v>
       </c>
       <c r="I10" s="33">
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/7dcc13a2-91b9-40ff-bac6-1a43c9a1d316_Lô_đất_ký_hiệu_CT-02_15_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/7dcc13a2-91b9-40ff-bac6-1a43c9a1d316_Lô_đất_ký_hiệu_CT-02_15_D800_19-03-2026.xlsx
@@ -112,7 +112,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -122,7 +122,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">10:15
@@ -142,7 +142,7 @@
     <t>11</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">10:55
@@ -152,7 +152,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">11:15
@@ -162,7 +162,7 @@
     <t>15</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:45
@@ -172,7 +172,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
